--- a/data/trans_bre/IP16B08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Habitat-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,16</t>
+          <t>0,0; 69,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 211,82</t>
+          <t>0,0; 222,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-82,56; 0,0</t>
+          <t>-83,59; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,56; 0,0</t>
+          <t>-83,59; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,01</t>
+          <t>0,0; 60,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 163,1</t>
+          <t>0,0; 150,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 7,14</t>
+          <t>-17,01; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,54</t>
+          <t>0,0; 22,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 7,62</t>
+          <t>-18,25; 7,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,12</t>
+          <t>0,0; 28,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Habitat-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,24</t>
+          <t>0,0; 70,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 222,25</t>
+          <t>0,0; 238,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,59; 0,0</t>
+          <t>-82,56; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,59; 0,0</t>
+          <t>-82,56; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,05</t>
+          <t>0,0; 60,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 150,29</t>
+          <t>0,0; 154,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 6,93</t>
+          <t>-16,63; 7,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,1</t>
+          <t>0,0; 25,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 7,38</t>
+          <t>-17,07; 7,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,46</t>
+          <t>0,0; 34,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
